--- a/data/b2_candoi/B2 Candói 07-2026.xlsx
+++ b/data/b2_candoi/B2 Candói 07-2026.xlsx
@@ -4878,20 +4878,20 @@
     </row>
     <row r="2">
       <c r="A2" s="7" t="n">
-        <v>46206</v>
+        <v>46208</v>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>Manutenção</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Manutenção preventiva das bombas</t>
+          <t>Salários do mês anterior</t>
         </is>
       </c>
       <c r="D2" s="16" t="n">
-        <v>1466.27</v>
+        <v>57823.79</v>
       </c>
     </row>
     <row r="3">
@@ -4900,183 +4900,183 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Salários do mês anterior</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
-        <v>57025.74</v>
+        <v>2623.42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
-        <v>46208</v>
+        <v>46213</v>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Sistemas e contabilidade</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Sistema de automação e contabilidade</t>
         </is>
       </c>
       <c r="D4" s="16" t="n">
-        <v>2931.87</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="n">
-        <v>46213</v>
+        <v>46215</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Material de limpeza e escritório</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
-        <v>1144.43</v>
+        <v>4164.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>46213</v>
+        <v>46215</v>
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Sistemas e contabilidade</t>
+          <t>Água e esgoto</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sistema de automação e contabilidade</t>
+          <t>Conta de água</t>
         </is>
       </c>
       <c r="D6" s="16" t="n">
-        <v>3200</v>
+        <v>1232.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="n">
-        <v>46215</v>
+        <v>46218</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Energia elétrica</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Conta de energia</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>3916.74</v>
+        <v>8232.459999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>46215</v>
+        <v>46218</v>
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Água e esgoto</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Conta de água</t>
+          <t>Placas, redes sociais e brindes</t>
         </is>
       </c>
       <c r="D8" s="16" t="n">
-        <v>855.03</v>
+        <v>886.78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Energia elétrica</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Conta de energia</t>
+          <t>Uniformes e EPI</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>8215.09</v>
+        <v>1104.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>46218</v>
+        <v>46222</v>
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Taxas de cartão</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Placas, redes sociais e brindes</t>
+          <t>Taxas das maquininhas (semana)</t>
         </is>
       </c>
       <c r="D10" s="16" t="n">
-        <v>978.98</v>
+        <v>4132.54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Folha de pagamento</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Uniformes e EPI</t>
+          <t>Encargos (INSS e FGTS)</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>1382.15</v>
+        <v>20119.58</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Outras despesas</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Monitoramento e alarme</t>
+          <t>Manutenção preventiva das bombas</t>
         </is>
       </c>
       <c r="D12" s="16" t="n">
-        <v>1055.3</v>
+        <v>2640.38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="n">
-        <v>46221</v>
+        <v>46227</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -5085,47 +5085,47 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manutenção do compressor de ar</t>
+          <t>Troca de filtros das bombas</t>
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>2032.6</v>
+        <v>2159.04</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>46222</v>
+        <v>46227</v>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Taxas de cartão</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Taxas das maquininhas (semana)</t>
+          <t>Tarifas bancárias</t>
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>3955.38</v>
+        <v>761.27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="n">
-        <v>46223</v>
+        <v>46227</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Folha de pagamento</t>
+          <t>Outras despesas</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Encargos (INSS e FGTS)</t>
+          <t>Monitoramento e alarme</t>
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>20196.74</v>
+        <v>1404.28</v>
       </c>
     </row>
     <row r="16">
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="D17" s="17" t="n">
-        <v>3993.15</v>
+        <v>4179.31</v>
       </c>
     </row>
     <row r="18">
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="D18" s="16" t="n">
-        <v>2730.62</v>
+        <v>2767.87</v>
       </c>
     </row>
   </sheetData>
